--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,26 +429,26 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -473,22 +473,22 @@
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>3</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -500,7 +500,7 @@
         <v>ANANAS E ZENZERO</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +508,7 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -525,16 +525,16 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -551,8 +551,8 @@
       <c r="G6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -565,46 +565,46 @@
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="str">
+        <v/>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -617,8 +617,8 @@
       <c r="C9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -643,8 +643,8 @@
       <c r="C10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
+      <c r="D10">
+        <v>2</v>
       </c>
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
@@ -663,8 +663,8 @@
       <c r="A11" t="str">
         <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>LEMON CURD</v>
@@ -689,14 +689,14 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12">
-        <v>2</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -721,8 +721,8 @@
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -748,7 +748,7 @@
         <v>ZABAIONE GELATO</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -819,8 +819,8 @@
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -831,14 +831,14 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17">
-        <v>1</v>
+      <c r="F17" t="str">
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
+      <c r="H17">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
+      <c r="F18">
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -871,8 +871,8 @@
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -935,8 +935,8 @@
       <c r="E21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
+      <c r="F21">
+        <v>3</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -949,8 +949,8 @@
       <c r="A22" t="str">
         <v>MONTBLANC</v>
       </c>
-      <c r="B22">
-        <v>2</v>
+      <c r="B22" t="str">
+        <v/>
       </c>
       <c r="C22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -967,16 +967,16 @@
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22">
-        <v>1</v>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -993,8 +993,8 @@
       <c r="G23" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
+      <c r="H23">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1019,8 +1019,8 @@
       <c r="G24" t="str">
         <v>MANDARINO</v>
       </c>
-      <c r="H24">
-        <v>1</v>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1079,8 +1079,8 @@
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27">
-        <v>1</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1149,8 +1149,8 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29">
-        <v>2</v>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1175,8 +1175,8 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1235,8 +1235,8 @@
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1279,8 +1279,8 @@
       <c r="G34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34">
-        <v>1</v>
+      <c r="H34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1306,15 +1306,15 @@
         <v>PERA</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36">
-        <v>1</v>
+      <c r="B36" t="str">
+        <v/>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1331,16 +1331,16 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36">
-        <v>2</v>
+      <c r="H36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37">
-        <v>2</v>
+      <c r="B37" t="str">
+        <v/>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1391,8 +1391,8 @@
       <c r="A39" t="str">
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
-      <c r="B39">
-        <v>1</v>
+      <c r="B39" t="str">
+        <v/>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1443,8 +1443,8 @@
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1496,7 +1496,7 @@
         <v>YOGURT</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 81</v>
+        <v>Totale vaschette: 106</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -430,25 +430,25 @@
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -456,25 +456,25 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -499,8 +499,8 @@
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4">
-        <v>1</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -525,8 +525,8 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>1</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -539,8 +539,8 @@
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -551,34 +551,34 @@
       <c r="G6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6">
-        <v>2</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="str">
+        <v/>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>CACHI</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -617,8 +617,8 @@
       <c r="C9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -643,14 +643,14 @@
       <c r="C10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10">
-        <v>2</v>
+      <c r="D10" t="str">
+        <v/>
       </c>
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="str">
+        <v/>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
@@ -689,8 +689,8 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12">
-        <v>3</v>
+      <c r="B12" t="str">
+        <v/>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -701,8 +701,8 @@
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="F12" t="str">
+        <v/>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -715,14 +715,14 @@
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>2</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -793,8 +793,8 @@
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -819,8 +819,8 @@
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17">
-        <v>2</v>
+      <c r="B17" t="str">
+        <v/>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -831,8 +831,8 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="F17">
+        <v>2</v>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20">
-        <v>1</v>
+      <c r="B20" t="str">
+        <v/>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21">
-        <v>1</v>
+      <c r="B21" t="str">
+        <v/>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -936,7 +936,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -967,16 +967,16 @@
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23">
-        <v>4</v>
+      <c r="B23" t="str">
+        <v/>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,7 +994,7 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>3</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1071,16 +1071,16 @@
       <c r="G26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26">
-        <v>1</v>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1149,16 +1149,16 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
         <v>POLLICINA</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1183,8 +1183,8 @@
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1227,16 +1227,16 @@
       <c r="G32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33">
-        <v>1</v>
+      <c r="B33" t="str">
+        <v/>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1287,8 +1287,8 @@
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35">
-        <v>1</v>
+      <c r="B35" t="str">
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1331,8 +1331,8 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1444,7 +1444,7 @@
         <v>TE VERDE MATCHA</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 106</v>
+        <v>Totale vaschette: 104</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -430,13 +430,13 @@
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
@@ -456,25 +456,25 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3">
-        <v>3</v>
+      <c r="F3" t="str">
+        <v/>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -507,8 +507,8 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>2</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -533,14 +533,14 @@
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -551,8 +551,8 @@
       <c r="G6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -560,7 +560,7 @@
         <v>CAFFE'</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -585,26 +585,26 @@
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -649,8 +649,8 @@
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
@@ -669,8 +669,8 @@
       <c r="C11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -689,8 +689,8 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -701,8 +701,8 @@
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
+      <c r="F12">
+        <v>4</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -721,8 +721,8 @@
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>1</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -794,7 +794,7 @@
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -831,22 +831,22 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17">
-        <v>2</v>
+      <c r="F17" t="str">
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="str">
+        <v/>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18">
-        <v>1</v>
+      <c r="F18" t="str">
+        <v/>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -872,7 +872,7 @@
         <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -909,8 +909,8 @@
       <c r="E20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
+      <c r="F20">
+        <v>1</v>
       </c>
       <c r="G20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -935,8 +935,8 @@
       <c r="E21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21">
-        <v>2</v>
+      <c r="F21" t="str">
+        <v/>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -961,14 +961,14 @@
       <c r="E22" t="str">
         <v>SACHER TORTE</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
+      <c r="F22">
+        <v>1</v>
       </c>
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1080,7 +1080,7 @@
         <v>PERE BELLE HELENE</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1158,7 +1158,7 @@
         <v>POLLICINA</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>1</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1228,7 +1228,7 @@
         <v>PAPAYA</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1254,7 +1254,7 @@
         <v>PASSION FRUIT</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1313,8 +1313,8 @@
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1332,15 +1332,15 @@
         <v>PESCHE AL VINO</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1443,8 +1443,8 @@
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41">
-        <v>2</v>
+      <c r="B41" t="str">
+        <v/>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1461,8 +1461,8 @@
       <c r="G41" t="str">
         <v>UVA E NOCI</v>
       </c>
-      <c r="H41" t="str">
-        <v/>
+      <c r="H41">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1495,8 +1495,8 @@
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43">
-        <v>1</v>
+      <c r="B43" t="str">
+        <v/>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 104</v>
+        <v>Totale vaschette: 112</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -430,25 +430,25 @@
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -456,25 +456,25 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -488,13 +488,13 @@
         <v>CREMA AGNESE</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
@@ -507,8 +507,8 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>3</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -525,16 +525,16 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
-      <c r="B6">
-        <v>2</v>
+      <c r="B6" t="str">
+        <v/>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -560,25 +560,25 @@
         <v>CAFFE'</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
+      <c r="F7">
+        <v>1</v>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         <v>COCCO CREMA</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -675,8 +675,8 @@
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
+      <c r="F11">
+        <v>1</v>
       </c>
       <c r="G11" t="str">
         <v>COCCO AL RUM</v>
@@ -695,34 +695,34 @@
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>1</v>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>1</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -805,8 +805,8 @@
       <c r="E16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
+      <c r="F16">
+        <v>1</v>
       </c>
       <c r="G16" t="str">
         <v>FICHI D INDIA</v>
@@ -819,8 +819,8 @@
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -831,22 +831,22 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="F17">
+        <v>3</v>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
+      <c r="F18">
+        <v>2</v>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -871,8 +871,8 @@
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19">
-        <v>1</v>
+      <c r="B19" t="str">
+        <v/>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -935,8 +935,8 @@
       <c r="E21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
+      <c r="F21">
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -967,16 +967,16 @@
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22">
-        <v>2</v>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>4</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,15 +994,15 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1019,8 +1019,8 @@
       <c r="G24" t="str">
         <v>MANDARINO</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
+      <c r="H24">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1046,7 +1046,7 @@
         <v>MANGO SOLE DI SICILIA</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1071,8 +1071,8 @@
       <c r="G26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1131,8 +1131,8 @@
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29">
-        <v>4</v>
+      <c r="B29" t="str">
+        <v/>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1158,7 +1158,7 @@
         <v>POLLICINA</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1175,16 +1175,16 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30">
-        <v>1</v>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31">
-        <v>1</v>
+      <c r="B31" t="str">
+        <v/>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1235,8 +1235,8 @@
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1254,7 +1254,7 @@
         <v>PASSION FRUIT</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1279,16 +1279,16 @@
       <c r="G34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1391,8 +1391,8 @@
       <c r="A39" t="str">
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>2</v>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1495,8 +1495,8 @@
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>3</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 112</v>
+        <v>Totale vaschette: 158</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -430,13 +430,13 @@
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
@@ -455,52 +455,52 @@
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3">
-        <v>7</v>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3">
-        <v>4</v>
+      <c r="F3" t="str">
+        <v/>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="H3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>4</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -508,13 +508,13 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5">
-        <v>1</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -525,8 +525,8 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>3</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -539,8 +539,8 @@
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -559,8 +559,8 @@
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>3</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -571,8 +571,8 @@
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="str">
+        <v/>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
@@ -586,13 +586,13 @@
         <v>COCCO CREMA</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8">
-        <v>1</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -669,14 +669,14 @@
       <c r="C11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
       </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="F11" t="str">
+        <v/>
       </c>
       <c r="G11" t="str">
         <v>COCCO AL RUM</v>
@@ -689,26 +689,26 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12">
-        <v>3</v>
+      <c r="B12" t="str">
+        <v/>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -721,8 +721,8 @@
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>3</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -748,7 +748,7 @@
         <v>ZABAIONE GELATO</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="str">
         <v>CIOCCOLATO UGANDA</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -794,7 +794,7 @@
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -805,8 +805,8 @@
       <c r="E16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" t="str">
+        <v/>
       </c>
       <c r="G16" t="str">
         <v>FICHI D INDIA</v>
@@ -831,8 +831,8 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17">
-        <v>3</v>
+      <c r="F17" t="str">
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18">
-        <v>2</v>
+      <c r="F18" t="str">
+        <v/>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -883,8 +883,8 @@
       <c r="E19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="F19">
-        <v>1</v>
+      <c r="F19" t="str">
+        <v/>
       </c>
       <c r="G19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -910,7 +910,7 @@
         <v>GIANDUIA VARIEGATA</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21">
-        <v>1</v>
+      <c r="B21" t="str">
+        <v/>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -936,7 +936,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -961,8 +961,8 @@
       <c r="E22" t="str">
         <v>SACHER TORTE</v>
       </c>
-      <c r="F22">
-        <v>1</v>
+      <c r="F22" t="str">
+        <v/>
       </c>
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -975,8 +975,8 @@
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23">
-        <v>4</v>
+      <c r="B23" t="str">
+        <v/>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,7 +994,7 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1002,7 +1002,7 @@
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>2</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1072,15 +1072,15 @@
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27">
-        <v>1</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1150,7 +1150,7 @@
         <v>MIRTILLO</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1158,7 +1158,7 @@
         <v>POLLICINA</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>1</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1228,15 +1228,15 @@
         <v>PAPAYA</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33">
-        <v>1</v>
+      <c r="B33" t="str">
+        <v/>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33">
-        <v>3</v>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1280,7 +1280,7 @@
         <v>PENSIERO</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1288,7 +1288,7 @@
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1306,7 +1306,7 @@
         <v>PERA</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1332,7 +1332,7 @@
         <v>PESCHE AL VINO</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1340,7 +1340,7 @@
         <v>SEADAS</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1392,7 +1392,7 @@
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 158</v>
+        <v>Totale vaschette: 103</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,8 +429,8 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>3</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
@@ -455,20 +455,20 @@
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>8</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
-        <v>2</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
@@ -481,26 +481,26 @@
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
       </c>
-      <c r="F4">
-        <v>2</v>
+      <c r="F4" t="str">
+        <v/>
       </c>
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -508,13 +508,13 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -540,7 +540,7 @@
         <v>CREMA CANNELLA</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -559,14 +559,14 @@
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -578,7 +578,7 @@
         <v>BANANA E LIME</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -586,13 +586,13 @@
         <v>COCCO CREMA</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>2</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
@@ -643,20 +643,20 @@
       <c r="C10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
+      <c r="D10">
+        <v>1</v>
       </c>
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="str">
+        <v/>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
       </c>
-      <c r="H10" t="str">
-        <v/>
+      <c r="H10">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -689,8 +689,8 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>3</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -702,7 +702,7 @@
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -715,14 +715,14 @@
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -780,13 +780,13 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
       </c>
-      <c r="H15">
-        <v>1</v>
+      <c r="H15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -794,7 +794,7 @@
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -838,7 +838,7 @@
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
+      <c r="F18">
+        <v>2</v>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -883,8 +883,8 @@
       <c r="E19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
+      <c r="F19">
+        <v>2</v>
       </c>
       <c r="G19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -936,7 +936,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -949,8 +949,8 @@
       <c r="A22" t="str">
         <v>MONTBLANC</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -967,16 +967,16 @@
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>NOCCIOLA</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>3</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,15 +994,15 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
-      <c r="B24">
-        <v>2</v>
+      <c r="B24" t="str">
+        <v/>
       </c>
       <c r="C24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1105,8 +1105,8 @@
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28">
-        <v>3</v>
+      <c r="B28" t="str">
+        <v/>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1123,8 +1123,8 @@
       <c r="G28" t="str">
         <v>MELONE</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1149,8 +1149,8 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29">
-        <v>2</v>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1158,7 +1158,7 @@
         <v>POLLICINA</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1227,16 +1227,16 @@
       <c r="G32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32">
-        <v>1</v>
+      <c r="H32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>3</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1279,8 +1279,8 @@
       <c r="G34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34">
-        <v>3</v>
+      <c r="H34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1313,8 +1313,8 @@
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36">
-        <v>1</v>
+      <c r="B36" t="str">
+        <v/>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1331,8 +1331,8 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36">
-        <v>3</v>
+      <c r="H36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -1340,7 +1340,7 @@
         <v>SEADAS</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1365,8 +1365,8 @@
       <c r="A38" t="str">
         <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
-      <c r="B38">
-        <v>1</v>
+      <c r="B38" t="str">
+        <v/>
       </c>
       <c r="C38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
@@ -1409,8 +1409,8 @@
       <c r="G39" t="str">
         <v>PUNCH PARADISE</v>
       </c>
-      <c r="H39" t="str">
-        <v/>
+      <c r="H39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1443,8 +1443,8 @@
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1487,8 +1487,8 @@
       <c r="G42" t="str">
         <v>UVA FRAGOLA E ZENZERO</v>
       </c>
-      <c r="H42">
-        <v>1</v>
+      <c r="H42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -1496,7 +1496,7 @@
         <v>YOGURT</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 103</v>
+        <v>Totale vaschette: 138</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,20 +429,20 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>5</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
@@ -456,7 +456,7 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -468,13 +468,13 @@
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="H3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>3</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -500,7 +500,7 @@
         <v>ANANAS E ZENZERO</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -508,33 +508,33 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>BUONGIORNO AMORE</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -559,14 +559,14 @@
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>1</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -578,15 +578,15 @@
         <v>BANANA E LIME</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>2</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -598,7 +598,7 @@
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
@@ -617,8 +617,8 @@
       <c r="C9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
+      <c r="D9">
+        <v>3</v>
       </c>
       <c r="E9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -649,8 +649,8 @@
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
@@ -669,8 +669,8 @@
       <c r="C11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -695,14 +695,14 @@
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12">
-        <v>2</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -715,20 +715,20 @@
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>1</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
+      <c r="F13">
+        <v>1</v>
       </c>
       <c r="G13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -794,7 +794,7 @@
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -838,7 +838,7 @@
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -858,7 +858,7 @@
         <v>FIOR DI CIOCCOLATO</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -883,8 +883,8 @@
       <c r="E19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="F19">
-        <v>2</v>
+      <c r="F19" t="str">
+        <v/>
       </c>
       <c r="G19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -909,8 +909,8 @@
       <c r="E20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20">
-        <v>2</v>
+      <c r="F20" t="str">
+        <v/>
       </c>
       <c r="G20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -936,7 +936,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -961,14 +961,14 @@
       <c r="E22" t="str">
         <v>SACHER TORTE</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
+      <c r="F22">
+        <v>1</v>
       </c>
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -976,7 +976,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,15 +994,15 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>1</v>
       </c>
       <c r="C24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>3</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1071,16 +1071,16 @@
       <c r="G26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26">
-        <v>3</v>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>3</v>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1105,8 +1105,8 @@
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>9</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1123,16 +1123,16 @@
       <c r="G28" t="str">
         <v>MELONE</v>
       </c>
-      <c r="H28">
-        <v>1</v>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>1</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1157,8 +1157,8 @@
       <c r="A30" t="str">
         <v>POLLICINA</v>
       </c>
-      <c r="B30">
-        <v>2</v>
+      <c r="B30" t="str">
+        <v/>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1175,16 +1175,16 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>1</v>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>2</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1227,8 +1227,8 @@
       <c r="G32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
+      <c r="H32">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1236,7 +1236,7 @@
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33">
-        <v>2</v>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1279,16 +1279,16 @@
       <c r="G34" t="str">
         <v>PENSIERO</v>
       </c>
-      <c r="H34" t="str">
-        <v/>
+      <c r="H34">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35">
-        <v>1</v>
+      <c r="B35" t="str">
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1313,8 +1313,8 @@
       <c r="A36" t="str">
         <v>RISO E VANIGLIA</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1340,7 +1340,7 @@
         <v>SEADAS</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1392,7 +1392,7 @@
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1444,7 +1444,7 @@
         <v>TE VERDE MATCHA</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1462,7 +1462,7 @@
         <v>UVA E NOCI</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 138</v>
+        <v>Totale vaschette: 158</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,14 +429,14 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>5</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2">
-        <v>2</v>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
@@ -456,25 +456,25 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3">
-        <v>5</v>
+      <c r="F3" t="str">
+        <v/>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -482,13 +482,13 @@
         <v>BASILICO NOCI E MIELE</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>4</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -500,21 +500,21 @@
         <v>ANANAS E ZENZERO</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>3</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -525,8 +525,8 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>4</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -539,8 +539,8 @@
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
       </c>
-      <c r="D6">
-        <v>2</v>
+      <c r="D6" t="str">
+        <v/>
       </c>
       <c r="E6" t="str">
         <v>CIOCCOLATO BIANCO</v>
@@ -552,21 +552,21 @@
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -577,16 +577,16 @@
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>3</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
@@ -597,8 +597,8 @@
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8">
-        <v>4</v>
+      <c r="F8" t="str">
+        <v/>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
@@ -617,8 +617,8 @@
       <c r="C9" t="str">
         <v>CREMA VANIGLIA</v>
       </c>
-      <c r="D9">
-        <v>3</v>
+      <c r="D9" t="str">
+        <v/>
       </c>
       <c r="E9" t="str">
         <v>CIOCCOLATO EQUADOR</v>
@@ -663,14 +663,14 @@
       <c r="A11" t="str">
         <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
-      <c r="B11">
-        <v>1</v>
+      <c r="B11" t="str">
+        <v/>
       </c>
       <c r="C11" t="str">
         <v>LEMON CURD</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -690,7 +690,7 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
@@ -702,7 +702,7 @@
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -794,7 +794,7 @@
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -805,8 +805,8 @@
       <c r="E16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
+      <c r="F16">
+        <v>1</v>
       </c>
       <c r="G16" t="str">
         <v>FICHI D INDIA</v>
@@ -831,14 +831,14 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="F17">
+        <v>3</v>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -871,8 +871,8 @@
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -883,8 +883,8 @@
       <c r="E19" t="str">
         <v>GIANDUIA</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
+      <c r="F19">
+        <v>2</v>
       </c>
       <c r="G19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20">
-        <v>2</v>
+      <c r="B20" t="str">
+        <v/>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21">
-        <v>2</v>
+      <c r="B21" t="str">
+        <v/>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -936,7 +936,7 @@
         <v>MOU LATTE SALATO</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -962,13 +962,13 @@
         <v>SACHER TORTE</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22">
-        <v>3</v>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -976,7 +976,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,7 +994,7 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1080,7 +1080,7 @@
         <v>PERE BELLE HELENE</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1149,8 +1149,8 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1184,7 +1184,7 @@
         <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1228,7 +1228,7 @@
         <v>PAPAYA</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1236,7 +1236,7 @@
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1287,8 +1287,8 @@
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1339,8 +1339,8 @@
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37">
-        <v>2</v>
+      <c r="B37" t="str">
+        <v/>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1409,8 +1409,8 @@
       <c r="G39" t="str">
         <v>PUNCH PARADISE</v>
       </c>
-      <c r="H39">
-        <v>2</v>
+      <c r="H39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1461,8 +1461,8 @@
       <c r="G41" t="str">
         <v>UVA E NOCI</v>
       </c>
-      <c r="H41">
-        <v>2</v>
+      <c r="H41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1495,8 +1495,8 @@
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43">
-        <v>1</v>
+      <c r="B43" t="str">
+        <v/>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 158</v>
+        <v>Totale vaschette: 146</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,8 +429,8 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
@@ -456,39 +456,39 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3">
-        <v>3</v>
+      <c r="D3" t="str">
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
+      <c r="F3">
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4">
-        <v>4</v>
+      <c r="D4" t="str">
+        <v/>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -507,14 +507,14 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>3</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5">
-        <v>2</v>
+      <c r="D5" t="str">
+        <v/>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
@@ -534,7 +534,7 @@
         <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -552,21 +552,21 @@
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -577,28 +577,28 @@
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>4</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="F8">
+        <v>3</v>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
@@ -670,7 +670,7 @@
         <v>LEMON CURD</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -695,20 +695,20 @@
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
       </c>
-      <c r="H12">
-        <v>1</v>
+      <c r="H12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -779,8 +779,8 @@
       <c r="E15" t="str">
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
-      <c r="F15">
-        <v>4</v>
+      <c r="F15" t="str">
+        <v/>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -793,8 +793,8 @@
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16">
-        <v>4</v>
+      <c r="B16" t="str">
+        <v/>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -820,7 +820,7 @@
         <v>LIQUIRIZIA</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -831,8 +831,8 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17">
-        <v>3</v>
+      <c r="F17" t="str">
+        <v/>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
@@ -845,8 +845,8 @@
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18">
-        <v>1</v>
+      <c r="B18" t="str">
+        <v/>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18">
-        <v>1</v>
+      <c r="F18" t="str">
+        <v/>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -872,7 +872,7 @@
         <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -962,7 +962,7 @@
         <v>SACHER TORTE</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
@@ -994,15 +994,15 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>NOCCIOLA, BURRO &amp; FIORI DI SALVIA</v>
       </c>
-      <c r="B24">
-        <v>1</v>
+      <c r="B24" t="str">
+        <v/>
       </c>
       <c r="C24" t="str">
         <v>GELATO DI PANETTONE</v>
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>6</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1079,8 +1079,8 @@
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27">
-        <v>2</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1105,8 +1105,8 @@
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28">
-        <v>2</v>
+      <c r="B28" t="str">
+        <v/>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1176,7 +1176,7 @@
         <v>MORA</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1184,7 +1184,7 @@
         <v>RICOTTA E AGRUMI</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1228,7 +1228,7 @@
         <v>PAPAYA</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1280,15 +1280,15 @@
         <v>PENSIERO</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35">
-        <v>1</v>
+      <c r="B35" t="str">
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1306,7 +1306,7 @@
         <v>PERA</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1331,16 +1331,16 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>1</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1392,7 +1392,7 @@
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1495,8 +1495,8 @@
       <c r="A43" t="str">
         <v>YOGURT</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>2</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 146</v>
+        <v>Totale vaschette: 118</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,8 +429,8 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
@@ -441,8 +441,8 @@
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="str">
+        <v/>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
@@ -456,7 +456,7 @@
         <v>BACIO DEL PRINCIPE</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
@@ -468,13 +468,13 @@
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -507,8 +507,8 @@
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5">
-        <v>3</v>
+      <c r="B5" t="str">
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -534,7 +534,7 @@
         <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -552,15 +552,15 @@
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
@@ -571,40 +571,40 @@
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
+      <c r="F7">
+        <v>2</v>
       </c>
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7">
-        <v>1</v>
+      <c r="H7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8">
-        <v>1</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -644,13 +644,13 @@
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="str">
+        <v/>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
@@ -690,19 +690,19 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12">
-        <v>3</v>
+      <c r="D12" t="str">
+        <v/>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12">
-        <v>4</v>
+      <c r="F12" t="str">
+        <v/>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -715,14 +715,14 @@
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="D13">
+        <v>2</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -779,8 +779,8 @@
       <c r="E15" t="str">
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="F15">
+        <v>1</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -793,8 +793,8 @@
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>4</v>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -820,7 +820,7 @@
         <v>LIQUIRIZIA</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -857,8 +857,8 @@
       <c r="E18" t="str">
         <v>FIOR DI CIOCCOLATO</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
+      <c r="F18">
+        <v>1</v>
       </c>
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
@@ -872,7 +872,7 @@
         <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -884,7 +884,7 @@
         <v>GIANDUIA</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="str">
         <v>FRAGOLINE DI BOSCO AL CALVADOS</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -935,8 +935,8 @@
       <c r="E21" t="str">
         <v>MOU LATTE SALATO</v>
       </c>
-      <c r="F21">
-        <v>2</v>
+      <c r="F21" t="str">
+        <v/>
       </c>
       <c r="G21" t="str">
         <v>HIBISCUS</v>
@@ -950,7 +950,7 @@
         <v>MONTBLANC</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -994,7 +994,7 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
+      <c r="H25">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1105,8 +1105,8 @@
       <c r="A28" t="str">
         <v>PISTACCHIO DI BRONTE</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>3</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1123,8 +1123,8 @@
       <c r="G28" t="str">
         <v>MELONE</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
+      <c r="H28">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1132,7 +1132,7 @@
         <v>PISTACCHIO SIRIANO</v>
       </c>
       <c r="B29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1150,7 +1150,7 @@
         <v>MIRTILLO</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1175,8 +1175,8 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30">
-        <v>2</v>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
+      <c r="H31">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1236,7 +1236,7 @@
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1287,8 +1287,8 @@
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1314,7 +1314,7 @@
         <v>RISO E VANIGLIA</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1332,7 +1332,7 @@
         <v>PESCHE AL VINO</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1444,7 +1444,7 @@
         <v>TE VERDE MATCHA</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1469,8 +1469,8 @@
       <c r="A42" t="str">
         <v>VENERE ROSA</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>1</v>
       </c>
       <c r="C42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 118</v>
+        <v>Totale vaschette: 144</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,8 +429,8 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>5</v>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
@@ -447,22 +447,22 @@
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3">
-        <v>8</v>
+      <c r="B3" t="str">
+        <v/>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
@@ -474,21 +474,21 @@
         <v>AMARENA</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="D4">
+        <v>4</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -499,16 +499,16 @@
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4">
-        <v>2</v>
+      <c r="H4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>BIANCANEVE</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
@@ -525,8 +525,8 @@
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
+      <c r="H5">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -534,7 +534,7 @@
         <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -560,13 +560,13 @@
         <v>CAFFE'</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7">
-        <v>2</v>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -577,28 +577,28 @@
       <c r="G7" t="str">
         <v>BANANA E LIME</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
+      <c r="H7">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8">
-        <v>4</v>
+      <c r="B8" t="str">
+        <v/>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="D8">
+        <v>3</v>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="str">
+        <v/>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
@@ -643,14 +643,14 @@
       <c r="C10" t="str">
         <v>CREMA ZENZERO MIELE DI CASTAGNO E LIMONE</v>
       </c>
-      <c r="D10">
-        <v>2</v>
+      <c r="D10" t="str">
+        <v/>
       </c>
       <c r="E10" t="str">
         <v>CIOCCOLATO KENTUCKY</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10" t="str">
         <v>COCCO</v>
@@ -669,8 +669,8 @@
       <c r="C11" t="str">
         <v>LEMON CURD</v>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="str">
+        <v/>
       </c>
       <c r="E11" t="str">
         <v>CIOCCOLATO LAPSANG SOUCHOUNG</v>
@@ -690,13 +690,13 @@
         <v>FIORDILATTE</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="D12">
+        <v>4</v>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
@@ -707,22 +707,22 @@
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="H12">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>FIORI DI LAVANDA E FRAGOLINE DI NEMI</v>
       </c>
-      <c r="B13">
-        <v>2</v>
+      <c r="B13" t="str">
+        <v/>
       </c>
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
@@ -780,7 +780,7 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
@@ -793,8 +793,8 @@
       <c r="A16" t="str">
         <v>LATTE MENTA E CIOCCOLATO</v>
       </c>
-      <c r="B16">
-        <v>4</v>
+      <c r="B16" t="str">
+        <v/>
       </c>
       <c r="C16" t="str">
         <v>speciali</v>
@@ -805,8 +805,8 @@
       <c r="E16" t="str">
         <v>CIOCCOLATO WASABI</v>
       </c>
-      <c r="F16">
-        <v>1</v>
+      <c r="F16" t="str">
+        <v/>
       </c>
       <c r="G16" t="str">
         <v>FICHI D INDIA</v>
@@ -819,8 +819,8 @@
       <c r="A17" t="str">
         <v>LIQUIRIZIA</v>
       </c>
-      <c r="B17">
-        <v>1</v>
+      <c r="B17" t="str">
+        <v/>
       </c>
       <c r="C17" t="str">
         <v>ANGURIA, GIN, ZUCCHERO DI CANNA &amp; SALE MALDON</v>
@@ -831,22 +831,22 @@
       <c r="E17" t="str">
         <v>ESTASI</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
+      <c r="F17">
+        <v>3</v>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>MANDORLA AL CARDAMOMO</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>1</v>
       </c>
       <c r="C18" t="str">
         <v>CASTAGNACCIO</v>
@@ -863,8 +863,8 @@
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
+      <c r="H18">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -872,7 +872,7 @@
         <v>MANDORLA BIANCA</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -898,7 +898,7 @@
         <v>MANDORLA E ARANCIA</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -909,8 +909,8 @@
       <c r="E20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
+      <c r="F20">
+        <v>1</v>
       </c>
       <c r="G20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -976,7 +976,7 @@
         <v>NOCCIOLA</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="str">
         <v>FIORI DI MAGNOLIA &amp; LIME</v>
@@ -994,7 +994,7 @@
         <v>LIMONE</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1045,8 +1045,8 @@
       <c r="G25" t="str">
         <v>MANGO SOLE DI SICILIA</v>
       </c>
-      <c r="H25">
-        <v>6</v>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1071,8 +1071,8 @@
       <c r="G26" t="str">
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
+      <c r="H26">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,8 +1097,8 @@
       <c r="G27" t="str">
         <v>MELOGRANO WONDERFUL</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="H27">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1131,8 +1131,8 @@
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29">
-        <v>5</v>
+      <c r="B29" t="str">
+        <v/>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1149,16 +1149,16 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29">
-        <v>1</v>
+      <c r="H29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
         <v>POLLICINA</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>3</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1175,16 +1175,16 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31">
-        <v>2</v>
+      <c r="B31" t="str">
+        <v/>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1201,8 +1201,8 @@
       <c r="G31" t="str">
         <v>PANACEA (LATTE DI MANDORLA MENTA &amp; GINSENG)</v>
       </c>
-      <c r="H31">
-        <v>2</v>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33">
-        <v>2</v>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1280,15 +1280,15 @@
         <v>PENSIERO</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35">
-        <v>2</v>
+      <c r="B35" t="str">
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1314,7 +1314,7 @@
         <v>RISO E VANIGLIA</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="str">
         <v>PESCA TABACCHIERA</v>
@@ -1331,16 +1331,16 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36">
-        <v>3</v>
+      <c r="H36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37">
-        <v>1</v>
+      <c r="B37" t="str">
+        <v/>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1409,8 +1409,8 @@
       <c r="G39" t="str">
         <v>PUNCH PARADISE</v>
       </c>
-      <c r="H39" t="str">
-        <v/>
+      <c r="H39">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1443,8 +1443,8 @@
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41">
-        <v>1</v>
+      <c r="B41" t="str">
+        <v/>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1470,7 +1470,7 @@
         <v>VENERE ROSA</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -1496,7 +1496,7 @@
         <v>YOGURT</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 144</v>
+        <v>Totale vaschette: 139</v>
       </c>
     </row>
   </sheetData>

--- a/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
+++ b/output/shocapp_ordini_settimanali_for_pdf_raw.xlsx
@@ -429,46 +429,46 @@
       <c r="A2" t="str">
         <v>ARACHIDI COCCO E CIOCCOLATO</v>
       </c>
-      <c r="B2">
-        <v>5</v>
+      <c r="B2" t="str">
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>CARROT CAKE</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>CIOCCOLATO</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2" t="str">
         <v>ALBICOCCA</v>
       </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="H2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>BACIO DEL PRINCIPE</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>7</v>
       </c>
       <c r="C3" t="str">
         <v>CHEESECAKE MIRTILLI</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="str">
         <v>CIOCCOLATO AL LATTE GELATO</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>AMARENA</v>
@@ -481,14 +481,14 @@
       <c r="A4" t="str">
         <v>BASILICO NOCI E MIELE</v>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" t="str">
+        <v/>
       </c>
       <c r="C4" t="str">
         <v>CREMA AGNESE</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
         <v>CIOCCOLATO AL PIMENTO</v>
@@ -499,8 +499,8 @@
       <c r="G4" t="str">
         <v>ANANAS E ZENZERO</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
+      <c r="H4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -508,25 +508,25 @@
         <v>BIANCANEVE</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="str">
         <v>CREMA BANANA CON CROCCANTINO CIOCCOLATO &amp; SESAMO</v>
       </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="D5">
+        <v>1</v>
       </c>
       <c r="E5" t="str">
         <v>CIOCCOLATO AL WHISKY</v>
       </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="F5" t="str">
+        <v/>
       </c>
       <c r="G5" t="str">
         <v>ANGURIA</v>
       </c>
-      <c r="H5">
-        <v>3</v>
+      <c r="H5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -534,7 +534,7 @@
         <v>BUONGIORNO AMORE</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>CREMA CANNELLA</v>
@@ -551,22 +551,22 @@
       <c r="G6" t="str">
         <v>AVOCADO LIME E VINO BIANCO</v>
       </c>
-      <c r="H6">
-        <v>2</v>
+      <c r="H6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>CAFFE'</v>
       </c>
-      <c r="B7">
-        <v>3</v>
+      <c r="B7" t="str">
+        <v/>
       </c>
       <c r="C7" t="str">
         <v>CREMA FRAGOLE E MANDORLE</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="str">
         <v>CIOCCOLATO CRUDO DEL PERU'</v>
@@ -578,33 +578,33 @@
         <v>BANANA E LIME</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>COCCO CREMA</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>3</v>
       </c>
       <c r="C8" t="str">
         <v>CREMA PASTICCIERA PARISI</v>
       </c>
-      <c r="D8">
-        <v>3</v>
+      <c r="D8" t="str">
+        <v/>
       </c>
       <c r="E8" t="str">
         <v>CIOCCOLATO E ARANCIA</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
+      <c r="F8">
+        <v>2</v>
       </c>
       <c r="G8" t="str">
         <v>CACHI</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
+      <c r="H8">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -655,16 +655,16 @@
       <c r="G10" t="str">
         <v>COCCO</v>
       </c>
-      <c r="H10">
-        <v>1</v>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>FINOCCHIO MIELE LIQUIRIZIA</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>LEMON CURD</v>
@@ -689,20 +689,20 @@
       <c r="A12" t="str">
         <v>FIORDILATTE</v>
       </c>
-      <c r="B12">
-        <v>4</v>
+      <c r="B12" t="str">
+        <v/>
       </c>
       <c r="C12" t="str">
         <v>SACRIPANTE</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="str">
         <v>CIOCCOLATO MADAGASCAR</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="str">
         <v>COCONUT RICE CAKE</v>
@@ -721,14 +721,14 @@
       <c r="C13" t="str">
         <v>TIRAMISU'</v>
       </c>
-      <c r="D13">
-        <v>1</v>
+      <c r="D13" t="str">
+        <v/>
       </c>
       <c r="E13" t="str">
         <v>CIOCCOLATO ROSEMARY</v>
       </c>
-      <c r="F13">
-        <v>1</v>
+      <c r="F13" t="str">
+        <v/>
       </c>
       <c r="G13" t="str">
         <v>DRACARYS (dragon fruit, fragole &amp; peperoncino)</v>
@@ -780,13 +780,13 @@
         <v>CIOCCOLATO VENEZUELA</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" t="str">
         <v>FICHI</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="H15">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -832,13 +832,13 @@
         <v>ESTASI</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="str">
         <v>FRAGOLA</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -863,16 +863,16 @@
       <c r="G18" t="str">
         <v>FRAGOLE DI TERRACINA &amp; CHAMPAGNE</v>
       </c>
-      <c r="H18">
-        <v>1</v>
+      <c r="H18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>MANDORLA BIANCA</v>
       </c>
-      <c r="B19">
-        <v>2</v>
+      <c r="B19" t="str">
+        <v/>
       </c>
       <c r="C19" t="str">
         <v>COTOGNATA</v>
@@ -897,8 +897,8 @@
       <c r="A20" t="str">
         <v>MANDORLA E ARANCIA</v>
       </c>
-      <c r="B20">
-        <v>2</v>
+      <c r="B20" t="str">
+        <v/>
       </c>
       <c r="C20" t="str">
         <v>CREMA COGNAC E NOCE MOSCATA</v>
@@ -909,8 +909,8 @@
       <c r="E20" t="str">
         <v>GIANDUIA VARIEGATA</v>
       </c>
-      <c r="F20">
-        <v>1</v>
+      <c r="F20" t="str">
+        <v/>
       </c>
       <c r="G20" t="str">
         <v>FRUTTI DI BOSCO (LAMPONE, RIBES, MORA, MIRTILLO)</v>
@@ -923,8 +923,8 @@
       <c r="A21" t="str">
         <v>MANDORLA TOSTATA</v>
       </c>
-      <c r="B21">
-        <v>1</v>
+      <c r="B21" t="str">
+        <v/>
       </c>
       <c r="C21" t="str">
         <v>CREMA DI FICHI SETTEMBRINI &amp; GRUE' DI LAMPONI</v>
@@ -950,7 +950,7 @@
         <v>MONTBLANC</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>CREMA ELISIR BORSCI &amp; PINOLI TOSTATI</v>
@@ -967,8 +967,8 @@
       <c r="G22" t="str">
         <v>LAMPONI SORBETTO</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -993,8 +993,8 @@
       <c r="G23" t="str">
         <v>LIMONE</v>
       </c>
-      <c r="H23">
-        <v>2</v>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1072,15 +1072,15 @@
         <v>MELA MANDORLA E CANNELLA</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>PERE BELLE HELENE</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>1</v>
       </c>
       <c r="C27" t="str">
         <v>MATCHA-BASILICO-AVOCADO &amp; PERLE DI FRUTTA</v>
@@ -1097,8 +1097,8 @@
       <c r="G27" t="str">
         <v>MELOGRANO WONDERFUL</v>
       </c>
-      <c r="H27">
-        <v>3</v>
+      <c r="H27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1106,7 +1106,7 @@
         <v>PISTACCHIO DI BRONTE</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" t="str">
         <v>MATE-LATE</v>
@@ -1123,16 +1123,16 @@
       <c r="G28" t="str">
         <v>MELONE</v>
       </c>
-      <c r="H28">
-        <v>2</v>
+      <c r="H28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>PISTACCHIO SIRIANO</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>2</v>
       </c>
       <c r="C29" t="str">
         <v>MOJITO ALLA AMARENA</v>
@@ -1149,8 +1149,8 @@
       <c r="G29" t="str">
         <v>MIRTILLO</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
+      <c r="H29">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1158,7 +1158,7 @@
         <v>POLLICINA</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>NON TI SCORDAR DI ME</v>
@@ -1175,16 +1175,16 @@
       <c r="G30" t="str">
         <v>MORA</v>
       </c>
-      <c r="H30">
-        <v>2</v>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>RICOTTA E AGRUMI</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>PASTIERA NAPOLETANA</v>
@@ -1227,16 +1227,16 @@
       <c r="G32" t="str">
         <v>PAPAYA</v>
       </c>
-      <c r="H32">
-        <v>2</v>
+      <c r="H32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>RICOTTA ROMANA, CACAO CRUDO &amp; PERA (LA-LA-LAND)</v>
       </c>
-      <c r="B33">
-        <v>1</v>
+      <c r="B33" t="str">
+        <v/>
       </c>
       <c r="C33" t="str">
         <v>PERA AL GORGONZOLA</v>
@@ -1253,8 +1253,8 @@
       <c r="G33" t="str">
         <v>PASSION FRUIT</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
+      <c r="H33">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1287,8 +1287,8 @@
       <c r="A35" t="str">
         <v>RICOTTA, MIELE E COCCO</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>1</v>
       </c>
       <c r="C35" t="str">
         <v>PESCA BIANCA AL BASILICO</v>
@@ -1306,7 +1306,7 @@
         <v>PERA</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1331,16 +1331,16 @@
       <c r="G36" t="str">
         <v>PESCHE AL VINO</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
+      <c r="H36">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v>SEADAS</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>POMODORO DATTERINO</v>
@@ -1365,8 +1365,8 @@
       <c r="A38" t="str">
         <v>STRACCHINO CON SALSA DI PERE AL MARSALA &amp; NOCI LARA</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>1</v>
       </c>
       <c r="C38" t="str">
         <v>RISO AL COCCO &amp; SALSA AL MANGO PICCANTE</v>
@@ -1392,7 +1392,7 @@
         <v>STRACCHINO, ALBICOCCHE AL ROSMARINO &amp; BRICIOLE DI CROSTATA</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="str">
         <v>ROSA KAEKADE E ARANCIA</v>
@@ -1409,8 +1409,8 @@
       <c r="G39" t="str">
         <v>PUNCH PARADISE</v>
       </c>
-      <c r="H39">
-        <v>2</v>
+      <c r="H39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1418,7 +1418,7 @@
         <v>STRACCIATELLA</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C40" t="str">
         <v>STRACCIATELLA AL FIOR DI RISO</v>
@@ -1443,8 +1443,8 @@
       <c r="A41" t="str">
         <v>TE VERDE MATCHA</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41" t="str">
         <v>TORRONE SALATO</v>
@@ -1469,8 +1469,8 @@
       <c r="A42" t="str">
         <v>VENERE ROSA</v>
       </c>
-      <c r="B42">
-        <v>2</v>
+      <c r="B42" t="str">
+        <v/>
       </c>
       <c r="C42" t="str">
         <v>VIRGIN BANANA (BANANA, COCCO LIMONE)</v>
@@ -1487,8 +1487,8 @@
       <c r="G42" t="str">
         <v>UVA FRAGOLA E ZENZERO</v>
       </c>
-      <c r="H42" t="str">
-        <v/>
+      <c r="H42">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1496,7 +1496,7 @@
         <v>YOGURT</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="str">
         <v>ZABAIONE VIN SANTO OCCHIO DI PERNICE</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Totale vaschette: 139</v>
+        <v>Totale vaschette: 118</v>
       </c>
     </row>
   </sheetData>
